--- a/Resource/Excel_Param/MaterialParam.xlsx
+++ b/Resource/Excel_Param/MaterialParam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D89F903B-0AED-4E5D-9AA4-C9CE65FE5FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE073C47-CFF2-49AF-9001-3EE89E831A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
+    <workbookView xWindow="555" yWindow="540" windowWidth="27435" windowHeight="14940" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="60">
   <si>
     <t>タグ</t>
     <phoneticPr fontId="1"/>
@@ -98,14 +98,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Player</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Resource/Texture/外壁S050.jpg</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Resource/Texture/DefaultN_Map.png</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -120,6 +112,138 @@
   <si>
     <t>Emsv_G</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Model/Player/textures/Soldier_Body_diffuse.png</t>
+  </si>
+  <si>
+    <t>Resource/Model/Player/textures/Soldier_Body_specular.png</t>
+  </si>
+  <si>
+    <t>Resource/Model/Player/textures/Soldier_Body_normal.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Model/Player/textures/Soldier_head_diffuse.png</t>
+  </si>
+  <si>
+    <t>Resource/Model/Player/textures/Soldier_head_normal.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Model/Player/textures/Soldier_head_specular.png</t>
+  </si>
+  <si>
+    <t>Bullet</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/rust_coarse_01_arm_1k.jpg</t>
+  </si>
+  <si>
+    <t>AssultRifle</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Soldier_body</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Soldier_head</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Light_Img.png</t>
+  </si>
+  <si>
+    <t>DirLight</t>
+  </si>
+  <si>
+    <t>Canonn</t>
+  </si>
+  <si>
+    <t>Resource/Model/Enemy/trader_ant_lowpoly.fbm/new_bake_ant.png</t>
+  </si>
+  <si>
+    <t>Resource/Model/Enemy/trader_ant_lowpoly.fbm/new_bake_ant_n.png</t>
+  </si>
+  <si>
+    <t>Ant</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>B_2</t>
+  </si>
+  <si>
+    <t>Resource/Model/b-2/textures/ggg_diffuseOriginal.jpeg</t>
+  </si>
+  <si>
+    <t>Resource/Model/b-2/textures/ggg_metallic.jpeg</t>
+  </si>
+  <si>
+    <t>Resource/Model/Claymore/Mat_Base_Color.png</t>
+  </si>
+  <si>
+    <t>Resource/Model/Claymore/Mat_Roughness.png</t>
+  </si>
+  <si>
+    <t>Resource/Model/Claymore/Mat_Normal_DirectX.png</t>
+  </si>
+  <si>
+    <t>Claymore</t>
+  </si>
+  <si>
+    <t>Building</t>
+  </si>
+  <si>
+    <t>Resource/Model/Building/01/texture/building5-lo.jpg</t>
+  </si>
+  <si>
+    <t>Resource/Texture/DefaultN_Map.png</t>
+  </si>
+  <si>
+    <t>MotherShip</t>
+  </si>
+  <si>
+    <t>Resource/Texture/metal_plate_02_diff_2k.jpg</t>
+  </si>
+  <si>
+    <t>Ground</t>
+  </si>
+  <si>
+    <t>Resource/Texture/aerial_grass_rock_diff_4k.png</t>
+  </si>
+  <si>
+    <t>Resource/Texture/aerial_grass_rock_nor_dx_4k.png</t>
+  </si>
+  <si>
+    <t>Resource/Texture/0191.png</t>
+  </si>
+  <si>
+    <t>Billboard</t>
+  </si>
+  <si>
+    <t>PointLight</t>
+  </si>
+  <si>
+    <t>Resource/Model/b-2/textures/ggg_normal.jpeg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PlayerModel</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Wall_W040.jpg</t>
+  </si>
+  <si>
+    <t>Resource/Texture/Wall_W040_n.png</t>
+  </si>
+  <si>
+    <t>Resource/Texture/Wall_S050.jpg</t>
+  </si>
+  <si>
+    <t>Resource/Texture/Wall_W030.jpg</t>
   </si>
 </sst>
 </file>
@@ -157,7 +281,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -208,13 +332,84 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="dashDot">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashDot">
+        <color auto="1"/>
+      </left>
+      <right style="dashDot">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashDot">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -226,6 +421,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -561,7 +771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{802585E2-AC86-45DE-82DA-DD2323601C8B}">
-  <dimension ref="A1:R2"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.25" style="3" customWidth="1"/>
@@ -573,44 +783,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="60" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="M1" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>10</v>
@@ -630,7 +840,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="B2" s="2">
         <v>0.4</v>
@@ -672,15 +882,799 @@
         <v>0</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="Q2" s="2">
         <v>-1</v>
       </c>
       <c r="R2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3">
+        <v>1</v>
+      </c>
+      <c r="J3" s="3">
+        <v>50</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0</v>
+      </c>
+      <c r="N3" s="3">
+        <v>0</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="R3" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>1</v>
+      </c>
+      <c r="F4" s="3">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1</v>
+      </c>
+      <c r="H4" s="3">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3">
+        <v>1</v>
+      </c>
+      <c r="J4" s="3">
+        <v>50</v>
+      </c>
+      <c r="K4" s="3">
+        <v>0</v>
+      </c>
+      <c r="L4" s="3">
+        <v>0</v>
+      </c>
+      <c r="M4" s="3">
+        <v>0</v>
+      </c>
+      <c r="N4" s="3">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="R4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3">
+        <v>1</v>
+      </c>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3">
+        <v>1</v>
+      </c>
+      <c r="J5" s="3">
+        <v>200</v>
+      </c>
+      <c r="K5" s="3">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3">
+        <v>1</v>
+      </c>
+      <c r="M5" s="3">
+        <v>1</v>
+      </c>
+      <c r="N5" s="3">
+        <v>50</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="P5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>-1</v>
+      </c>
+      <c r="R5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3">
+        <v>1</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="3">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3">
+        <v>1</v>
+      </c>
+      <c r="J6" s="3">
+        <v>100</v>
+      </c>
+      <c r="K6" s="3">
+        <v>0</v>
+      </c>
+      <c r="L6" s="3">
+        <v>0</v>
+      </c>
+      <c r="M6" s="3">
+        <v>0</v>
+      </c>
+      <c r="N6" s="3">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="P6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q6" s="2">
+        <v>-1</v>
+      </c>
+      <c r="R6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3">
+        <v>1</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3">
+        <v>1</v>
+      </c>
+      <c r="H7" s="3">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1</v>
+      </c>
+      <c r="J7" s="3">
+        <v>100</v>
+      </c>
+      <c r="K7" s="3">
+        <v>1</v>
+      </c>
+      <c r="L7" s="3">
+        <v>1</v>
+      </c>
+      <c r="M7" s="3">
+        <v>1</v>
+      </c>
+      <c r="N7" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="P7" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q7" s="2">
+        <v>-1</v>
+      </c>
+      <c r="R7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3">
+        <v>1</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="3">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1</v>
+      </c>
+      <c r="J8" s="3">
+        <v>20</v>
+      </c>
+      <c r="K8" s="3">
+        <v>0</v>
+      </c>
+      <c r="L8" s="3">
+        <v>1</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>200</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q8" s="2">
+        <v>-1</v>
+      </c>
+      <c r="R8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="G9" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="H9" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3">
+        <v>100</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9" s="3">
+        <v>0</v>
+      </c>
+      <c r="M9" s="3">
+        <v>0</v>
+      </c>
+      <c r="N9" s="3">
+        <v>0</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>-1</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A10" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3">
+        <v>1</v>
+      </c>
+      <c r="H10" s="3">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1</v>
+      </c>
+      <c r="J10" s="3">
+        <v>100</v>
+      </c>
+      <c r="K10" s="3">
+        <v>0</v>
+      </c>
+      <c r="L10" s="3">
+        <v>0</v>
+      </c>
+      <c r="M10" s="3">
+        <v>0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="R10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
+        <v>1</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="3">
+        <v>1</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3">
+        <v>200</v>
+      </c>
+      <c r="K11" s="3">
+        <v>0</v>
+      </c>
+      <c r="L11" s="3">
+        <v>0</v>
+      </c>
+      <c r="M11" s="3">
+        <v>0</v>
+      </c>
+      <c r="N11" s="3">
+        <v>0</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="3">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3">
+        <v>1</v>
+      </c>
+      <c r="D12" s="3">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2">
+        <v>150</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0</v>
+      </c>
+      <c r="L12" s="3">
+        <v>0</v>
+      </c>
+      <c r="M12" s="3">
+        <v>0</v>
+      </c>
+      <c r="N12" s="3">
+        <v>0</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q12" s="2">
+        <v>-1</v>
+      </c>
+      <c r="R12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="3">
+        <v>1</v>
+      </c>
+      <c r="C13" s="3">
+        <v>1</v>
+      </c>
+      <c r="D13" s="3">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3">
+        <v>1</v>
+      </c>
+      <c r="F13" s="3">
+        <v>1</v>
+      </c>
+      <c r="G13" s="3">
+        <v>1</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2">
+        <v>150</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0</v>
+      </c>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q13" s="2">
+        <v>-1</v>
+      </c>
+      <c r="R13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="3">
+        <v>1</v>
+      </c>
+      <c r="C14" s="3">
+        <v>1</v>
+      </c>
+      <c r="D14" s="3">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1</v>
+      </c>
+      <c r="G14" s="3">
+        <v>1</v>
+      </c>
+      <c r="H14" s="3">
+        <v>1</v>
+      </c>
+      <c r="I14" s="3">
+        <v>1</v>
+      </c>
+      <c r="J14" s="3">
+        <v>50</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q14" s="2">
+        <v>-1</v>
+      </c>
+      <c r="R14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B15" s="3">
+        <v>1</v>
+      </c>
+      <c r="C15" s="3">
+        <v>1</v>
+      </c>
+      <c r="D15" s="3">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3">
+        <v>1</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1</v>
+      </c>
+      <c r="H15" s="3">
+        <v>1</v>
+      </c>
+      <c r="I15" s="3">
+        <v>1</v>
+      </c>
+      <c r="J15" s="3">
+        <v>50</v>
+      </c>
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P15" s="2">
+        <v>-1</v>
+      </c>
+      <c r="Q15" s="2">
+        <v>-1</v>
+      </c>
+      <c r="R15" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="3">
+        <v>1</v>
+      </c>
+      <c r="C16" s="3">
+        <v>1</v>
+      </c>
+      <c r="D16" s="3">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3">
+        <v>1</v>
+      </c>
+      <c r="F16" s="3">
+        <v>1</v>
+      </c>
+      <c r="G16" s="3">
+        <v>1</v>
+      </c>
+      <c r="H16" s="3">
+        <v>1</v>
+      </c>
+      <c r="I16" s="3">
+        <v>1</v>
+      </c>
+      <c r="J16" s="3">
+        <v>50</v>
+      </c>
+      <c r="K16" s="3">
+        <v>1</v>
+      </c>
+      <c r="L16" s="3">
+        <v>1</v>
+      </c>
+      <c r="M16" s="3">
+        <v>1</v>
+      </c>
+      <c r="N16" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q16" s="2">
+        <v>-1</v>
+      </c>
+      <c r="R16" s="2">
         <v>0</v>
       </c>
     </row>

--- a/Resource/Excel_Param/MaterialParam.xlsx
+++ b/Resource/Excel_Param/MaterialParam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\Resource\Excel_Param\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3\Documents\DX11_EDF_3DGame\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE073C47-CFF2-49AF-9001-3EE89E831A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC224734-3B25-4606-9EB5-7D43B8731303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="555" yWindow="540" windowWidth="27435" windowHeight="14940" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
+    <workbookView xWindow="2370" yWindow="1065" windowWidth="25320" windowHeight="11295" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,9 +27,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -211,9 +212,6 @@
     <t>Ground</t>
   </si>
   <si>
-    <t>Resource/Texture/aerial_grass_rock_diff_4k.png</t>
-  </si>
-  <si>
     <t>Resource/Texture/aerial_grass_rock_nor_dx_4k.png</t>
   </si>
   <si>
@@ -244,6 +242,10 @@
   </si>
   <si>
     <t>Resource/Texture/Wall_W030.jpg</t>
+  </si>
+  <si>
+    <t>Resource/Texture/water_surface02.png</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -840,7 +842,7 @@
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2">
         <v>0.4</v>
@@ -882,7 +884,7 @@
         <v>0</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P2" s="2" t="s">
         <v>15</v>
@@ -1106,7 +1108,7 @@
         <v>0</v>
       </c>
       <c r="O6" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="P6" s="2">
         <v>-1</v>
@@ -1218,10 +1220,10 @@
         <v>200</v>
       </c>
       <c r="O8" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P8" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="Q8" s="2">
         <v>-1</v>
@@ -1333,7 +1335,7 @@
         <v>37</v>
       </c>
       <c r="P10" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q10" s="3" t="s">
         <v>38</v>
@@ -1539,25 +1541,25 @@
         <v>1</v>
       </c>
       <c r="J14" s="3">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="K14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" s="3">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="O14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="P14" s="3" t="s">
         <v>49</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>50</v>
       </c>
       <c r="Q14" s="2">
         <v>-1</v>
@@ -1568,7 +1570,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B15" s="3">
         <v>1</v>
@@ -1610,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="O15" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P15" s="2">
         <v>-1</v>
@@ -1624,7 +1626,7 @@
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" s="3">
         <v>1</v>
@@ -1666,10 +1668,10 @@
         <v>0.1</v>
       </c>
       <c r="O16" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="P16" s="3" t="s">
         <v>56</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="Q16" s="2">
         <v>-1</v>
@@ -1681,5 +1683,6 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Resource/Excel_Param/MaterialParam.xlsx
+++ b/Resource/Excel_Param/MaterialParam.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student3\Documents\DX11_EDF_3DGame\Resource\Excel_Param\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edama\Documents\GitHub\DX11_EDF_3DGame\DX11_3D_Game_Test\Resource\Excel_Param\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC224734-3B25-4606-9EB5-7D43B8731303}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0F21A1-8F42-4F27-A4DF-777068313FDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2370" yWindow="1065" windowWidth="25320" windowHeight="11295" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
+    <workbookView xWindow="885" yWindow="1755" windowWidth="27435" windowHeight="14940" xr2:uid="{970EDF6D-C319-4BDE-B500-23E062F4BBAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,15 +29,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="66">
   <si>
     <t>タグ</t>
     <phoneticPr fontId="1"/>
@@ -245,6 +242,30 @@
   </si>
   <si>
     <t>Resource/Texture/water_surface02.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Decal_BulletHole</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/BulletHole.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/BulletHole_n.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Decal_Ant_Splash</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Acid_n.png</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Resource/Texture/Acid.png</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -773,7 +794,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{802585E2-AC86-45DE-82DA-DD2323601C8B}">
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="13.25" style="3" customWidth="1"/>
@@ -1680,6 +1701,118 @@
         <v>0</v>
       </c>
     </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A17" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1</v>
+      </c>
+      <c r="C17" s="3">
+        <v>1</v>
+      </c>
+      <c r="D17" s="3">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3">
+        <v>1</v>
+      </c>
+      <c r="F17" s="3">
+        <v>1</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1</v>
+      </c>
+      <c r="I17" s="3">
+        <v>1</v>
+      </c>
+      <c r="J17" s="3">
+        <v>100</v>
+      </c>
+      <c r="K17" s="3">
+        <v>1</v>
+      </c>
+      <c r="L17" s="3">
+        <v>1</v>
+      </c>
+      <c r="M17" s="3">
+        <v>1</v>
+      </c>
+      <c r="N17" s="3">
+        <v>1</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q17" s="3">
+        <v>-1</v>
+      </c>
+      <c r="R17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.4">
+      <c r="A18" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="3">
+        <v>1</v>
+      </c>
+      <c r="C18" s="3">
+        <v>1</v>
+      </c>
+      <c r="D18" s="3">
+        <v>1</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1</v>
+      </c>
+      <c r="G18" s="3">
+        <v>1</v>
+      </c>
+      <c r="H18" s="3">
+        <v>1</v>
+      </c>
+      <c r="I18" s="3">
+        <v>1</v>
+      </c>
+      <c r="J18" s="3">
+        <v>100</v>
+      </c>
+      <c r="K18" s="3">
+        <v>1</v>
+      </c>
+      <c r="L18" s="3">
+        <v>1</v>
+      </c>
+      <c r="M18" s="3">
+        <v>1</v>
+      </c>
+      <c r="N18" s="3">
+        <v>1</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-1</v>
+      </c>
+      <c r="R18" s="3">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
